--- a/data/trans_camb/IP19C05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Edad-trans_camb.xlsx
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,15</t>
+          <t>-3,04; 1,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,0</t>
+          <t>-3,86; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,56</t>
+          <t>-2,59; 1,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,0</t>
+          <t>-4,25; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,35</t>
+          <t>-1,69; 1,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,0</t>
+          <t>-2,77; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,55</t>
+          <t>0,42; 7,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,52</t>
+          <t>-0,84; 3,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,65</t>
+          <t>-2,7; 2,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,31</t>
+          <t>-3,89; 1,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 3,78</t>
+          <t>-0,42; 3,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,75</t>
+          <t>-1,63; 1,76</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,92; 1092,57</t>
+          <t>-56,99; 896,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,08; 495,47</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,7</t>
+          <t>-0,81; 4,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 7,01</t>
+          <t>0,26; 6,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,74</t>
+          <t>-0,27; 5,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 6,49</t>
+          <t>0,34; 6,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,49</t>
+          <t>0,11; 3,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,4</t>
+          <t>1,15; 5,47</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,6; 1138,37</t>
+          <t>-64,11; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,68; 1250,4</t>
+          <t>-25,34; 2187,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,9; —</t>
+          <t>-62,44; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 733,32</t>
+          <t>-22,89; 903,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,99; 1162,14</t>
+          <t>21,54; 1396,7</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,45</t>
+          <t>0,2; 3,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,32</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,22</t>
+          <t>-0,63; 2,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,12</t>
+          <t>-0,69; 2,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,3</t>
+          <t>0,15; 2,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,27</t>
+          <t>0,05; 2,28</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 902,71</t>
+          <t>-7,26; 948,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 836,63</t>
+          <t>-10,95; 904,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 522,94</t>
+          <t>-47,01; 524,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,87; 496,75</t>
+          <t>-52,76; 479,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,29; 421,86</t>
+          <t>0,5; 370,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,03; 411,11</t>
+          <t>-11,9; 346,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Edad-trans_camb.xlsx
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,15</t>
+          <t>-2,51; 1,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,0</t>
+          <t>-4,26; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,6</t>
+          <t>-3,44; 1,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,0</t>
+          <t>-4,76; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,26</t>
+          <t>-1,62; 1,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,0</t>
+          <t>-2,46; 0,0</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,13</t>
+          <t>0,41; 6,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,6</t>
+          <t>-0,83; 3,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,69</t>
+          <t>-2,97; 2,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,36</t>
+          <t>-3,75; 1,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,49</t>
+          <t>-0,63; 3,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,76</t>
+          <t>-1,41; 1,87</t>
         </is>
       </c>
     </row>
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 896,78</t>
+          <t>-50,84; 997,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,42; —</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 4,89</t>
+          <t>-0,71; 4,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,75</t>
+          <t>0,31; 7,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 5,04</t>
+          <t>-0,26; 4,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,17</t>
+          <t>0,37; 6,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,64</t>
+          <t>0,06; 3,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,47</t>
+          <t>1,02; 5,4</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,11; —</t>
+          <t>-68,6; 1257,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 2187,96</t>
+          <t>-40,35; 1600,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,44; —</t>
+          <t>-27,04; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 903,46</t>
+          <t>-9,42; 896,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,54; 1396,7</t>
+          <t>29,82; 1164,4</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,51</t>
+          <t>0,31; 3,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,05; 3,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,02</t>
+          <t>-0,53; 2,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,13</t>
+          <t>-0,55; 2,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,31</t>
+          <t>0,17; 2,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,28</t>
+          <t>0,1; 2,17</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 948,17</t>
+          <t>-12,08; 812,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 904,66</t>
+          <t>-22,92; 717,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,01; 524,91</t>
+          <t>-51,66; 594,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 479,87</t>
+          <t>-52,98; 707,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,5; 370,74</t>
+          <t>1,89; 396,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 346,45</t>
+          <t>-7,59; 410,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C05-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C05-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,85</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,16</t>
+          <t>-2,81; 1,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,0</t>
+          <t>-4,23; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,58</t>
+          <t>-2,39; 1,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,0</t>
+          <t>-4,22; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,27</t>
+          <t>-1,66; 1,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,0</t>
+          <t>-2,84; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,17 +825,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-8,23%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-25,1%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-8,23%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,59</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>2,98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1,21</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,46</t>
+          <t>-2,81; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,54</t>
+          <t>-4,24; 1,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,32</t>
+          <t>0,41; 6,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,26</t>
+          <t>-0,94; 3,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,65</t>
+          <t>-0,41; 3,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,87</t>
+          <t>-1,62; 1,75</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-39,69%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>460,39%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>187,46%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-39,69%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 997,46</t>
+          <t>-53,92; 1092,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-78,42; —</t>
+          <t>-89,08; 495,47</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,83</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>3,08</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,83</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,46</t>
+          <t>-0,35; 4,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,01</t>
+          <t>0,17; 6,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,47</t>
+          <t>-0,76; 4,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,82</t>
+          <t>0,04; 7,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,64</t>
+          <t>-0,13; 3,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,4</t>
+          <t>1,06; 5,4</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>226,64%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>381,66%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>126,37%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>239,38%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>226,64%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>381,66%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,6; 1257,41</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 1600,64</t>
+          <t>-47,9; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,6; 1138,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,04; —</t>
+          <t>-44,68; 1250,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 896,63</t>
+          <t>-22,18; 733,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,82; 1164,4</t>
+          <t>12,99; 1162,14</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1,55</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,54</t>
+          <t>-0,61; 2,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,53</t>
+          <t>-0,66; 2,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,18</t>
+          <t>0,2; 3,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,36</t>
+          <t>0,14; 3,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,22</t>
+          <t>0,17; 2,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,17</t>
+          <t>0,09; 2,27</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>71,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>171,83%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>160,17%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>74,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>71,24%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 812,05</t>
+          <t>-54,01; 522,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 717,05</t>
+          <t>-54,87; 496,75</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 594,21</t>
+          <t>-5,47; 902,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 707,1</t>
+          <t>-15,93; 836,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,89; 396,99</t>
+          <t>5,29; 421,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 410,21</t>
+          <t>2,03; 411,11</t>
         </is>
       </c>
     </row>
